--- a/www/terminologies/ValueSet-JDV-J71-ProfessionFonction-MSSante.xlsx
+++ b/www/terminologies/ValueSet-JDV-J71-ProfessionFonction-MSSante.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="128">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20231030120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-30T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -337,12 +337,6 @@
     <t>Préparateur en pharmacie (officine)</t>
   </si>
   <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>Auxiliaire de vie sociale</t>
-  </si>
-  <si>
     <t>319</t>
   </si>
   <si>
@@ -365,12 +359,6 @@
   </si>
   <si>
     <t>Assistant familial</t>
-  </si>
-  <si>
-    <t>323</t>
-  </si>
-  <si>
-    <t>Aide médico-psychologique (AMP)</t>
   </si>
   <si>
     <t>324</t>
@@ -877,7 +865,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1110,34 +1098,18 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>128</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J71-ProfessionFonction-MSSante.xlsx
+++ b/www/terminologies/ValueSet-JDV-J71-ProfessionFonction-MSSante.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="132">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20231030120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2023-10-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -337,6 +337,12 @@
     <t>Préparateur en pharmacie (officine)</t>
   </si>
   <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>Auxiliaire de vie sociale</t>
+  </si>
+  <si>
     <t>319</t>
   </si>
   <si>
@@ -359,6 +365,12 @@
   </si>
   <si>
     <t>Assistant familial</t>
+  </si>
+  <si>
+    <t>323</t>
+  </si>
+  <si>
+    <t>Aide médico-psychologique (AMP)</t>
   </si>
   <si>
     <t>324</t>
@@ -865,7 +877,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1098,18 +1110,34 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>70</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="B30" t="s" s="2">
-        <v>127</v>
+      <c r="B32" t="s" s="2">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
